--- a/config/playernumber.xlsx
+++ b/config/playernumber.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$231</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -1096,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G232"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -3987,7 +3987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:7">
       <c r="A145" s="2">
         <v>218</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:7">
       <c r="A146" s="2">
         <v>219</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:7">
       <c r="A147" s="2">
         <v>220</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:7">
       <c r="A148" s="2">
         <v>221</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:7">
       <c r="A149" s="2">
         <v>222</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:7">
       <c r="A150" s="2">
         <v>223</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:7">
       <c r="A151" s="2">
         <v>224</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:7">
       <c r="A152" s="2">
         <v>225</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:7">
       <c r="A153" s="2">
         <v>226</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:7">
       <c r="A154" s="2">
         <v>228</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:7">
       <c r="A156" s="2">
         <v>230</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:7">
       <c r="A158" s="2">
         <v>232</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:7">
       <c r="A159" s="2">
         <v>233</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:7">
       <c r="A160" s="2">
         <v>234</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:7">
       <c r="A163" s="2">
         <v>237</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:7">
       <c r="A165" s="2">
         <v>240</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:7">
       <c r="A167" s="2">
         <v>241</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:7">
       <c r="A168" s="2">
         <v>242</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:7">
       <c r="A169" s="2">
         <v>243</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:7">
       <c r="A170" s="2">
         <v>244</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:7">
       <c r="A171" s="2">
         <v>245</v>
       </c>
@@ -5616,8 +5616,8 @@
       <c r="D218" s="8">
         <v>169419</v>
       </c>
-      <c r="E218" s="2" t="s">
-        <v>10</v>
+      <c r="E218" s="2">
+        <v>3</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>9</v>
@@ -5626,12 +5626,331 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="5:5">
-      <c r="E219" s="2"/>
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
+        <v>292</v>
+      </c>
+      <c r="B219" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C219" s="7">
+        <v>45969</v>
+      </c>
+      <c r="D219" s="8">
+        <v>156432</v>
+      </c>
+      <c r="E219" s="2">
+        <v>1</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
+        <v>312</v>
+      </c>
+      <c r="B220" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C220" s="7">
+        <v>45979</v>
+      </c>
+      <c r="D220" s="8">
+        <v>160729</v>
+      </c>
+      <c r="E220" s="2">
+        <v>3</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
+        <v>313</v>
+      </c>
+      <c r="B221" s="7">
+        <v>45981</v>
+      </c>
+      <c r="C221" s="7">
+        <v>45989</v>
+      </c>
+      <c r="D221" s="8">
+        <v>157447</v>
+      </c>
+      <c r="E221" s="2">
+        <v>4</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>293</v>
+      </c>
+      <c r="B222" s="7">
+        <v>45991</v>
+      </c>
+      <c r="C222" s="7">
+        <v>46000</v>
+      </c>
+      <c r="D222" s="8">
+        <v>151274</v>
+      </c>
+      <c r="E222" s="2">
+        <v>13</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>294</v>
+      </c>
+      <c r="B223" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C223" s="7">
+        <v>46010</v>
+      </c>
+      <c r="D223" s="8">
+        <v>60545</v>
+      </c>
+      <c r="E223" s="2">
+        <v>8</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>295</v>
+      </c>
+      <c r="B224" s="7">
+        <v>46012</v>
+      </c>
+      <c r="C224" s="7">
+        <v>46019</v>
+      </c>
+      <c r="D224" s="8">
+        <v>126929</v>
+      </c>
+      <c r="E224" s="2">
+        <v>2</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>296</v>
+      </c>
+      <c r="B225" s="7">
+        <v>46021</v>
+      </c>
+      <c r="C225" s="7">
+        <v>46029</v>
+      </c>
+      <c r="D225" s="8">
+        <v>139814</v>
+      </c>
+      <c r="E225" s="2">
+        <v>3</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>297</v>
+      </c>
+      <c r="B226" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C226" s="7">
+        <v>46040</v>
+      </c>
+      <c r="D226" s="8">
+        <v>170899</v>
+      </c>
+      <c r="E226" s="2">
+        <v>2</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
+        <v>298</v>
+      </c>
+      <c r="B227" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C227" s="7">
+        <v>46051</v>
+      </c>
+      <c r="D227" s="8">
+        <v>141207</v>
+      </c>
+      <c r="E227" s="2">
+        <v>3</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
+        <v>300</v>
+      </c>
+      <c r="B228" s="7">
+        <v>46053</v>
+      </c>
+      <c r="C228" s="7">
+        <v>46062</v>
+      </c>
+      <c r="D228" s="8">
+        <v>137065</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
+        <v>299</v>
+      </c>
+      <c r="B229" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C229" s="7">
+        <v>46073</v>
+      </c>
+      <c r="D229" s="8">
+        <v>159812</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
+        <v>301</v>
+      </c>
+      <c r="B230" s="7">
+        <v>46075</v>
+      </c>
+      <c r="C230" s="7">
+        <v>46084</v>
+      </c>
+      <c r="D230" s="8">
+        <v>144103</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
+        <v>302</v>
+      </c>
+      <c r="B231" s="7">
+        <v>46086</v>
+      </c>
+      <c r="C231" s="7">
+        <v>46095</v>
+      </c>
+      <c r="D231" s="8">
+        <v>117319</v>
+      </c>
+      <c r="E231" s="2">
+        <v>2</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>303</v>
+      </c>
+      <c r="B232" s="7">
+        <v>46097</v>
+      </c>
+      <c r="C232" s="7">
+        <v>46106</v>
+      </c>
+      <c r="D232" s="8">
+        <v>113776</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F217" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F231" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -5651,7 +5970,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F247"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -9407,62 +9726,466 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="6:6">
-      <c r="F180" s="2"/>
-    </row>
-    <row r="181" spans="6:6">
-      <c r="F181" s="2"/>
-    </row>
-    <row r="182" spans="6:6">
-      <c r="F182" s="2"/>
-    </row>
-    <row r="183" spans="6:6">
-      <c r="F183" s="2"/>
-    </row>
-    <row r="184" spans="6:6">
-      <c r="F184" s="2"/>
-    </row>
-    <row r="185" spans="6:6">
-      <c r="F185" s="2"/>
-    </row>
-    <row r="186" spans="6:6">
-      <c r="F186" s="2"/>
-    </row>
-    <row r="187" spans="6:6">
-      <c r="F187" s="2"/>
-    </row>
-    <row r="188" spans="6:6">
-      <c r="F188" s="2"/>
-    </row>
-    <row r="189" spans="6:6">
-      <c r="F189" s="2"/>
-    </row>
-    <row r="190" spans="6:6">
-      <c r="F190" s="2"/>
-    </row>
-    <row r="191" spans="6:6">
-      <c r="F191" s="2"/>
-    </row>
-    <row r="192" spans="6:6">
-      <c r="F192" s="2"/>
-    </row>
-    <row r="193" spans="6:6">
-      <c r="F193" s="2"/>
-    </row>
-    <row r="194" spans="6:6">
+    <row r="180" spans="1:6">
+      <c r="A180" s="2">
+        <v>292</v>
+      </c>
+      <c r="B180" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C180" s="7">
+        <v>45969</v>
+      </c>
+      <c r="D180" s="3">
+        <v>39138</v>
+      </c>
+      <c r="E180" s="5">
+        <f>D180/B服!D219</f>
+        <v>0.250191776618595</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="2">
+        <v>312</v>
+      </c>
+      <c r="B181" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C181" s="7">
+        <v>45979</v>
+      </c>
+      <c r="D181" s="3">
+        <v>36830</v>
+      </c>
+      <c r="E181" s="5">
+        <f>D181/B服!D220</f>
+        <v>0.229143465087196</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="2">
+        <v>313</v>
+      </c>
+      <c r="B182" s="7">
+        <v>45981</v>
+      </c>
+      <c r="C182" s="7">
+        <v>45989</v>
+      </c>
+      <c r="D182" s="3">
+        <v>34899</v>
+      </c>
+      <c r="E182" s="5">
+        <f>D182/B服!D221</f>
+        <v>0.221655541229747</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" s="2">
+        <v>293</v>
+      </c>
+      <c r="B183" s="7">
+        <v>45991</v>
+      </c>
+      <c r="C183" s="7">
+        <v>46000</v>
+      </c>
+      <c r="D183" s="3">
+        <v>36026</v>
+      </c>
+      <c r="E183" s="5">
+        <f>D183/B服!D222</f>
+        <v>0.238150640559515</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" s="2">
+        <v>294</v>
+      </c>
+      <c r="B184" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C184" s="7">
+        <v>46010</v>
+      </c>
+      <c r="D184" s="3">
+        <v>8407</v>
+      </c>
+      <c r="E184" s="5">
+        <f>D184/B服!D223</f>
+        <v>0.138855396812288</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="2">
+        <v>295</v>
+      </c>
+      <c r="B185" s="7">
+        <v>46012</v>
+      </c>
+      <c r="C185" s="7">
+        <v>46019</v>
+      </c>
+      <c r="D185" s="3">
+        <v>33387</v>
+      </c>
+      <c r="E185" s="5">
+        <f>D185/B服!D224</f>
+        <v>0.263036815857684</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="2">
+        <v>296</v>
+      </c>
+      <c r="B186" s="7">
+        <v>46021</v>
+      </c>
+      <c r="C186" s="7">
+        <v>46029</v>
+      </c>
+      <c r="D186" s="3">
+        <v>38374</v>
+      </c>
+      <c r="E186" s="5">
+        <f>D186/B服!D225</f>
+        <v>0.274464645886678</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="2">
+        <v>297</v>
+      </c>
+      <c r="B187" s="7">
+        <v>46031</v>
+      </c>
+      <c r="C187" s="7">
+        <v>46040</v>
+      </c>
+      <c r="D187" s="3">
+        <v>46392</v>
+      </c>
+      <c r="E187" s="5">
+        <f>D187/B服!D226</f>
+        <v>0.271458580799186</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="2">
+        <v>298</v>
+      </c>
+      <c r="B188" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C188" s="7">
+        <v>46051</v>
+      </c>
+      <c r="D188" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E188" s="5">
+        <f>D188/B服!D227</f>
+        <v>0.325592923863548</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="2">
+        <v>300</v>
+      </c>
+      <c r="B189" s="7">
+        <v>46053</v>
+      </c>
+      <c r="C189" s="7">
+        <v>46062</v>
+      </c>
+      <c r="D189" s="3">
+        <v>60051</v>
+      </c>
+      <c r="E189" s="5">
+        <f>D189/B服!D228</f>
+        <v>0.438120599715463</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="2">
+        <v>299</v>
+      </c>
+      <c r="B190" s="7">
+        <v>46064</v>
+      </c>
+      <c r="C190" s="7">
+        <v>46073</v>
+      </c>
+      <c r="D190" s="3">
+        <v>67034</v>
+      </c>
+      <c r="E190" s="5">
+        <f>D190/B服!D229</f>
+        <v>0.419455360048056</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="2">
+        <v>301</v>
+      </c>
+      <c r="B191" s="7">
+        <v>46075</v>
+      </c>
+      <c r="C191" s="7">
+        <v>46084</v>
+      </c>
+      <c r="D191" s="3">
+        <v>52585</v>
+      </c>
+      <c r="E191" s="5">
+        <f>D191/B服!D230</f>
+        <v>0.364912597239475</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" s="2">
+        <v>302</v>
+      </c>
+      <c r="B192" s="7">
+        <v>46086</v>
+      </c>
+      <c r="C192" s="7">
+        <v>46095</v>
+      </c>
+      <c r="D192" s="3">
+        <v>35635</v>
+      </c>
+      <c r="E192" s="5">
+        <f>D192/B服!D231</f>
+        <v>0.303744491514588</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" s="2">
+        <v>303</v>
+      </c>
+      <c r="B193" s="7">
+        <v>46097</v>
+      </c>
+      <c r="C193" s="7">
+        <v>46106</v>
+      </c>
+      <c r="D193" s="3">
+        <v>34715</v>
+      </c>
+      <c r="E193" s="5">
+        <f>D193/B服!D232</f>
+        <v>0.305117072141752</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2"/>
       <c r="F194" s="2"/>
     </row>
-    <row r="195" spans="6:6">
+    <row r="195" spans="1:6">
+      <c r="A195" s="2"/>
       <c r="F195" s="2"/>
     </row>
-    <row r="196" spans="6:6">
+    <row r="196" spans="1:6">
+      <c r="A196" s="2"/>
       <c r="F196" s="2"/>
     </row>
-    <row r="197" spans="6:6">
+    <row r="197" spans="1:6">
+      <c r="A197" s="2"/>
       <c r="F197" s="2"/>
     </row>
-    <row r="198" spans="6:6">
+    <row r="198" spans="1:6">
+      <c r="A198" s="2"/>
       <c r="F198" s="2"/>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2"/>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2"/>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2"/>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2"/>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2"/>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2"/>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2"/>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2"/>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2"/>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2"/>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="2"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="2"/>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="2"/>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="2"/>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="2"/>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="2"/>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="2"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="2"/>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="2"/>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="2"/>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="2"/>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="2"/>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="2"/>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="2"/>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="2"/>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="2"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="2"/>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="2"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="2"/>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="2"/>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="2"/>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="2"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="2"/>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="2"/>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="2"/>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="2"/>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="2"/>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="2"/>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="2"/>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="2"/>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="2"/>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="2"/>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="2"/>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="2"/>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="2"/>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="2"/>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="2"/>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="2"/>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="2"/>
     </row>
   </sheetData>
   <sortState ref="A2:F134">
